--- a/Visa2026.Module/Resources/Templates/Excel/_merge_test_output.xlsx
+++ b/Visa2026.Module/Resources/Templates/Excel/_merge_test_output.xlsx
@@ -16,7 +16,7 @@
     <x:sheet name="Лист1" sheetId="2" r:id="rId1"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm.Print_Area" localSheetId="0">Лист1!$D$1:$P$26</x:definedName>
+    <x:definedName name="_xlnm.Print_Area" localSheetId="0">Лист1!$D$1:$P$11</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="152511"/>
 </x:workbook>
@@ -86,10 +86,7 @@
  </x:t>
   </x:si>
   <x:si>
-    <x:t>19.02.2026
-06.08.2026
-(A1691452)
-köp gezeklik</x:t>
+    <x:t xml:space="preserve">Çakylyk , </x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -105,51 +102,6 @@
   </x:si>
   <x:si>
     <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -383,7 +335,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="21">
+  <x:cellXfs count="22">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -442,6 +394,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="3">
@@ -860,7 +816,7 @@
       <x:c r="O4" s="12" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P4" s="13" t="s">
+      <x:c r="P4" s="21" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
@@ -904,8 +860,8 @@
       <x:c r="O5" s="12" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P5" s="13" t="s">
-        <x:v>23</x:v>
+      <x:c r="P5" s="21" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:20">
@@ -948,744 +904,84 @@
       <x:c r="O6" s="12" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P6" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:20">
-      <x:c r="C7" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D7" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E7" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F7" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G7" s="10" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H7" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I7" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J7" s="10" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K7" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="L7" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M7" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="N7" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="O7" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P7" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:20">
-      <x:c r="C8" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E8" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F8" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G8" s="10" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H8" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I8" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J8" s="10" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K8" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="L8" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M8" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="N8" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="O8" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P8" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:20">
-      <x:c r="C9" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D9" s="9" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E9" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F9" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G9" s="10" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H9" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I9" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J9" s="10" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K9" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="L9" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M9" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="N9" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="O9" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P9" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:20">
-      <x:c r="C10" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D10" s="9" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E10" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F10" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G10" s="10" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H10" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I10" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J10" s="10" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K10" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="L10" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M10" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="N10" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="O10" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P10" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:20">
-      <x:c r="C11" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D11" s="9" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E11" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F11" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G11" s="10" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H11" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I11" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J11" s="10" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K11" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="L11" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M11" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="N11" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="O11" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P11" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:20">
-      <x:c r="C12" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D12" s="9" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E12" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F12" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G12" s="10" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H12" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I12" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J12" s="10" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K12" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="L12" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M12" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="N12" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="O12" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P12" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:20">
-      <x:c r="C13" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D13" s="9" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E13" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F13" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G13" s="10" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H13" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I13" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J13" s="10" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K13" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="L13" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M13" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="N13" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="O13" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P13" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:20">
-      <x:c r="C14" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D14" s="9" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E14" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F14" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G14" s="10" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H14" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I14" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J14" s="10" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K14" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="L14" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M14" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="N14" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="O14" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P14" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:20">
-      <x:c r="C15" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D15" s="9" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E15" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F15" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G15" s="10" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H15" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I15" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J15" s="10" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K15" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="L15" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M15" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="N15" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="O15" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P15" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:20">
-      <x:c r="C16" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D16" s="9" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E16" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F16" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G16" s="10" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H16" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I16" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J16" s="10" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K16" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="L16" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M16" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="N16" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="O16" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P16" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:20">
-      <x:c r="C17" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D17" s="9" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E17" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F17" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G17" s="10" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H17" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I17" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J17" s="10" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K17" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="L17" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M17" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="N17" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="O17" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P17" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:20">
-      <x:c r="C18" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D18" s="9" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E18" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F18" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G18" s="10" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H18" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I18" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J18" s="10" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K18" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="L18" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M18" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="N18" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="O18" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P18" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:20">
-      <x:c r="C19" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D19" s="9" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E19" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F19" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G19" s="10" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H19" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I19" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J19" s="10" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K19" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="L19" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M19" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="N19" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="O19" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P19" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:20">
-      <x:c r="C20" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D20" s="9" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E20" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F20" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G20" s="10" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H20" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I20" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J20" s="10" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K20" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="L20" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M20" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="N20" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="O20" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P20" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:20">
-      <x:c r="C21" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D21" s="9" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E21" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F21" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G21" s="10" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H21" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I21" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J21" s="10" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K21" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="L21" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M21" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="N21" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="O21" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P21" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:20" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <x:c r="E22" s="17" t="s">
+      <x:c r="P6" s="21" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:20" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <x:c r="E7" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F22" s="17"/>
-      <x:c r="G22" s="17"/>
-      <x:c r="H22" s="17"/>
-      <x:c r="I22" s="17"/>
-      <x:c r="J22" s="17"/>
-      <x:c r="K22" s="17"/>
-      <x:c r="L22" s="19" t="s">
+      <x:c r="F7" s="17"/>
+      <x:c r="G7" s="17"/>
+      <x:c r="H7" s="17"/>
+      <x:c r="I7" s="17"/>
+      <x:c r="J7" s="17"/>
+      <x:c r="K7" s="17"/>
+      <x:c r="L7" s="19" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="M22" s="19"/>
-      <x:c r="N22" s="19"/>
-      <x:c r="O22" s="19"/>
-    </x:row>
-    <x:row r="23" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <x:c r="E23" s="18"/>
-      <x:c r="F23" s="18"/>
-      <x:c r="G23" s="18"/>
-      <x:c r="H23" s="18"/>
-      <x:c r="I23" s="18"/>
-      <x:c r="J23" s="18"/>
-      <x:c r="K23" s="18"/>
-      <x:c r="L23" s="20"/>
-      <x:c r="M23" s="20"/>
-      <x:c r="N23" s="20"/>
-      <x:c r="O23" s="20"/>
-    </x:row>
-    <x:row r="24" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <x:c r="E24" s="18"/>
-      <x:c r="F24" s="18"/>
-      <x:c r="G24" s="18"/>
-      <x:c r="H24" s="18"/>
-      <x:c r="I24" s="18"/>
-      <x:c r="J24" s="18"/>
-      <x:c r="K24" s="18"/>
-      <x:c r="L24" s="20"/>
-      <x:c r="M24" s="20"/>
-      <x:c r="N24" s="20"/>
-      <x:c r="O24" s="20"/>
-    </x:row>
-    <x:row r="25" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <x:c r="E25" s="18"/>
-      <x:c r="F25" s="18"/>
-      <x:c r="G25" s="18"/>
-      <x:c r="H25" s="18"/>
-      <x:c r="I25" s="18"/>
-      <x:c r="J25" s="18"/>
-      <x:c r="K25" s="18"/>
-      <x:c r="L25" s="20"/>
-      <x:c r="M25" s="20"/>
-      <x:c r="N25" s="20"/>
-      <x:c r="O25" s="20"/>
-    </x:row>
-    <x:row r="29" spans="1:20" x14ac:dyDescent="0.25">
-      <x:c r="G29" s="8"/>
-    </x:row>
-    <x:row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <x:c r="G30" s="8"/>
-    </x:row>
-    <x:row r="34" spans="1:20" x14ac:dyDescent="0.25">
-      <x:c r="G34" s="8"/>
-    </x:row>
-    <x:row r="35" spans="1:20" x14ac:dyDescent="0.25">
-      <x:c r="G35" s="8"/>
+      <x:c r="M7" s="19"/>
+      <x:c r="N7" s="19"/>
+      <x:c r="O7" s="19"/>
+    </x:row>
+    <x:row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <x:c r="E8" s="18"/>
+      <x:c r="F8" s="18"/>
+      <x:c r="G8" s="18"/>
+      <x:c r="H8" s="18"/>
+      <x:c r="I8" s="18"/>
+      <x:c r="J8" s="18"/>
+      <x:c r="K8" s="18"/>
+      <x:c r="L8" s="20"/>
+      <x:c r="M8" s="20"/>
+      <x:c r="N8" s="20"/>
+      <x:c r="O8" s="20"/>
+    </x:row>
+    <x:row r="9" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <x:c r="E9" s="18"/>
+      <x:c r="F9" s="18"/>
+      <x:c r="G9" s="18"/>
+      <x:c r="H9" s="18"/>
+      <x:c r="I9" s="18"/>
+      <x:c r="J9" s="18"/>
+      <x:c r="K9" s="18"/>
+      <x:c r="L9" s="20"/>
+      <x:c r="M9" s="20"/>
+      <x:c r="N9" s="20"/>
+      <x:c r="O9" s="20"/>
+    </x:row>
+    <x:row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <x:c r="E10" s="18"/>
+      <x:c r="F10" s="18"/>
+      <x:c r="G10" s="18"/>
+      <x:c r="H10" s="18"/>
+      <x:c r="I10" s="18"/>
+      <x:c r="J10" s="18"/>
+      <x:c r="K10" s="18"/>
+      <x:c r="L10" s="20"/>
+      <x:c r="M10" s="20"/>
+      <x:c r="N10" s="20"/>
+      <x:c r="O10" s="20"/>
+    </x:row>
+    <x:row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <x:c r="G14" s="8"/>
+    </x:row>
+    <x:row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <x:c r="G15" s="8"/>
+    </x:row>
+    <x:row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <x:c r="G19" s="8"/>
+    </x:row>
+    <x:row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <x:c r="G20" s="8"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells count="4">
     <x:mergeCell ref="G1:P1"/>
     <x:mergeCell ref="E2:P2"/>
-    <x:mergeCell ref="E22:K25"/>
-    <x:mergeCell ref="L22:O25"/>
+    <x:mergeCell ref="E7:K10"/>
+    <x:mergeCell ref="L7:O10"/>
   </x:mergeCells>
   <x:phoneticPr fontId="2" type="noConversion"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
